--- a/excel/read_kythi.xlsx
+++ b/excel/read_kythi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VISUAL\my-project\QuanLyQuiz\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{429916B6-458C-493C-8487-A4732113AF4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{940B928D-F539-4A84-B993-DA183696D6D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5108B01A-2AA9-407C-82C2-F89BB3BA43F8}"/>
   </bookViews>
@@ -60,12 +60,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -88,9 +95,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -429,18 +437,18 @@
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.1796875" customWidth="1"/>
+    <col min="3" max="3" width="21.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
